--- a/processed_ruby_restored_xlsx/sc218_ノノＡ：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc218_ノノＡ：遊園地.ss.xlsx
@@ -744,9 +744,9 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan, Rin-chan, and Rurichiyo-chan... that would
-make one circuit, so how about we try splitting into
-teams from next time？」</t>
+          <t>「Miru-chan, Rin-chan, and Rurichiyo-chan... that
+would make one circuit, so how about we try splitting
+into teams from next time？」</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -947,8 +947,9 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>If we split into groups, everyone would have more time
-to do as they like, so it shouldn’t be a bad idea.</t>
+          <t>If we split into groups, everyone would have more
+time to do as they like, so it shouldn’t be a bad
+idea.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1145,8 +1146,9 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>She probably doesn’t know my exact intentions, but she
-must feel proud she managed to get the better of me.</t>
+          <t>She probably doesn’t know my exact intentions, but
+she must feel proud she managed to get the better of
+me.</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1440,8 +1442,8 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>Then she twisted her head as if thinking hard, staring
-at me very intently.</t>
+          <t>Then she twisted her head as if thinking hard,
+staring at me very intently.</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1778,7 +1780,8 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan stops speaking there and steps closer to me.</t>
+          <t>Nono-chan stops speaking there and steps closer to
+me.</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1883,8 +1886,8 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Even though everyone's in the back seats, saying we're
-alone together... was just a turn of phrase.</t>
+          <t>Even though everyone's in the back seats, saying
+we're alone together... was just a turn of phrase.</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2007,8 +2010,9 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>When I think back to when we first met, we've gotten a
-lot closer... I especially feel that way these days.</t>
+          <t>When I think back to when we first met, we've gotten
+a lot closer... I especially feel that way these
+days.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2357,8 +2361,9 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>And Nono-chan, who had climbed up, seemed surprised at
-her own action and was blushing with embarrassment.</t>
+          <t>And Nono-chan, who had climbed up, seemed surprised
+at her own action and was blushing with
+embarrassment.</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2482,8 +2487,8 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan stirred, thinking she wanted to make me feel
-a little more embarrassed.</t>
+          <t>Nono-chan stirred, thinking she wanted to make me
+feel a little more embarrassed.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2712,8 +2717,8 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... if you’re this close, I can’t hold back... Is
-that wrong？」</t>
+          <t>「Yeah... if you’re this close, I can’t hold back...
+Is that wrong？」</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2835,8 +2840,8 @@
       <c r="B155" s="1" t="inlineStr">
         <is>
           <t>When I asked for a kiss in a clingy way, Nono-chan
-hesitated a bit, but to my surprise she nodded without
-much fuss.</t>
+hesitated a bit, but to my surprise she nodded
+without much fuss.</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -3143,8 +3148,8 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, smooch, smooch... sssmoo...！ Hah... smooch！ Smo,
-smoochoo！ Fnu...」</t>
+          <t>「Mmm, smooch, smooch... sssmoo...！ Hah... smooch！
+Smo, smoochoo！ Fnu...」</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3266,8 +3271,8 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>While convincing herself, and yet coming to seek me of
-her own accord, Nono-chan is just so adorable.</t>
+          <t>While convincing herself, and yet coming to seek me
+of her own accord, Nono-chan is just so adorable.</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3671,8 +3676,8 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>While I lick that away, I savor it thoroughly from the
-inside of her lips to the surface of her teeth.</t>
+          <t>While I lick that away, I savor it thoroughly from
+the inside of her lips to the surface of her teeth.</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3884,8 +3889,8 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>This time Nono-chan reaches up and sucks back, licking
-my tongue away.</t>
+          <t>This time Nono-chan reaches up and sucks back,
+licking my tongue away.</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -4039,8 +4044,9 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>Finally unable to hold back any longer, Nono-chan gave
-a sharp little jolt and buried her face in my chest.</t>
+          <t>Finally unable to hold back any longer, Nono-chan
+gave a sharp little jolt and buried her face in my
+chest.</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4193,8 +4199,8 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>Her mouth's just hanging open, saliva thickly spilling
-around it.</t>
+          <t>Her mouth's just hanging open, saliva thickly
+spilling around it.</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4562,7 +4568,8 @@
       <c r="B267" s="1" t="inlineStr">
         <is>
           <t>Even with vague back-and-forths, because we're aware
-of each other, Nono-chan gets more and more flustered.</t>
+of each other, Nono-chan gets more and more
+flustered.</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -5002,8 +5009,8 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>「I want to do it with Mui-sensei... bu-but, ba-baah...
-I can't... hold it in...」</t>
+          <t>「I want to do it with Mui-sensei... bu-but,
+ba-baah... I can't... hold it in...」</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5491,8 +5498,8 @@
       <c r="B328" s="1" t="inlineStr">
         <is>
           <t>Because her clothes had come undone while she was
-searching for the penis, Nono-chan let out a surprised
-sound.</t>
+searching for the penis, Nono-chan let out a
+surprised sound.</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5523,8 +5530,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>After all, my arousal and the erection of my penis had
-already reached their peak.</t>
+          <t>After all, my arousal and the erection of my penis
+had already reached their peak.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5892,8 +5899,8 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t>With that declaration, I gently lower Nono-chan's body
-down...</t>
+          <t>With that declaration, I gently lower Nono-chan's
+body down...</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -6091,8 +6098,8 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>She's probably getting anxious because it won't go in,
-but that seems to ramp up her excitement too.</t>
+          <t>She's probably getting anxious because it won't go
+in, but that seems to ramp up her excitement too.</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -6137,8 +6144,9 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>If my guess is right, just the tip rubbing her between
-her legs is making lewd sounds escape from her...</t>
+          <t>If my guess is right, just the tip rubbing her
+between her legs is making lewd sounds escape from
+her...</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6533,7 +6541,8 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t>「Aahh！ All at once... nn, hah！ It's all the way in...」</t>
+          <t>「Aahh！ All at once... nn, hah！ It's all the way
+in...」</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6640,8 +6649,8 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>...Nono-chan couldn't stop trembling from the pleasure
-of the insertion either.</t>
+          <t>...Nono-chan couldn't stop trembling from the
+pleasure of the insertion either.</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6748,8 +6757,8 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>More than that, didn't I just make a louder noise than
-I intended？</t>
+          <t>More than that, didn't I just make a louder noise
+than I intended？</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -7024,8 +7033,8 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t>But now that it's come this far, my hips move on their
-own.</t>
+          <t>But now that it's come this far, my hips move on
+their own.</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -7636,8 +7645,8 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>As I stoke her shame, Nono-chan can't help but let out
-sweet sounds.</t>
+          <t>As I stoke her shame, Nono-chan can't help but let
+out sweet sounds.</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7804,8 +7813,8 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>I snapped back, but I could feel my cheek twitching on
-its own.</t>
+          <t>I snapped back, but I could feel my cheek twitching
+on its own.</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -8155,7 +8164,8 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t>But unexpectedly, Nono-chan doesn't answer the kisses.</t>
+          <t>But unexpectedly, Nono-chan doesn't answer the
+kisses.</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -8170,8 +8180,8 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t>She's probably holding back her voice herself, staying
-tense to keep control.</t>
+          <t>She's probably holding back her voice herself,
+staying tense to keep control.</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -8327,8 +8337,8 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>Since she couldn't speak, Nono-chan gently offered her
-tongue instead.</t>
+          <t>Since she couldn't speak, Nono-chan gently offered
+her tongue instead.</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8682,8 +8692,8 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>After Nono-chan grinned, she kissed me again this time
-with pure feeling.</t>
+          <t>After Nono-chan grinned, she kissed me again this
+time with pure feeling.</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -8837,8 +8847,8 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... Janitor-sensei... smooch, mmm...！ Ahh, uaaa...
-mmm, smooch.」</t>
+          <t>「Mmm... Janitor-sensei... smooch, mmm...！ Ahh,
+uaaa... mmm, smooch.」</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -9680,8 +9690,8 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan doesn't seem to have the luxury of that; she
-just starts focusing on holding herself back.</t>
+          <t>Nono-chan doesn't seem to have the luxury of that;
+she just starts focusing on holding herself back.</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -9788,8 +9798,8 @@
       </c>
       <c r="B608" s="1" t="inlineStr">
         <is>
-          <t>I meant to relax her, but instead Nono-chan completely
-broke down.</t>
+          <t>I meant to relax her, but instead Nono-chan
+completely broke down.</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -9819,8 +9829,8 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>「Fuaa... there, ahhh, mmm, mmm-ah！ Hgh... kuh！ It's so
-intense... ah, haa...！」</t>
+          <t>「Fuaa... there, ahhh, mmm, mmm-ah！ Hgh... kuh！ It's
+so intense... ah, haa...！」</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -9914,8 +9924,8 @@
       </c>
       <c r="B616" s="1" t="inlineStr">
         <is>
-          <t>In one rush she nears her limit, and Nono-chan's voice
-shoots up loud.</t>
+          <t>In one rush she nears her limit, and Nono-chan's
+voice shoots up loud.</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -10036,8 +10046,9 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>Our breathing grew ragged, and when I realized neither
-of us could hold out any longer, I made my final push.</t>
+          <t>Our breathing grew ragged, and when I realized
+neither of us could hold out any longer, I made my
+final push.</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -10464,8 +10475,9 @@
       </c>
       <c r="B652" s="1" t="inlineStr">
         <is>
-          <t>And then Nono-chan reached her climax too, her vaginal
-muscles twitching as they clenched down on me.</t>
+          <t>And then Nono-chan reached her climax too, her
+vaginal muscles twitching as they clenched down on
+me.</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -10651,8 +10663,8 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>Her pussy twitched and pulsed in small jerks again and
-again as it stroked my penis.</t>
+          <t>Her pussy twitched and pulsed in small jerks again
+and again as it stroked my penis.</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -11323,9 +11335,9 @@
       </c>
       <c r="B708" s="1" t="inlineStr">
         <is>
-          <t>I was so turned on I almost forgot everything else, so
-I'm not confident, but I figured there was no need to
-make her anxious.</t>
+          <t>I was so turned on I almost forgot everything else,
+so I'm not confident, but I figured there was no need
+to make her anxious.</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -11508,8 +11520,8 @@
       </c>
       <c r="B720" s="1" t="inlineStr">
         <is>
-          <t>But it seemed that what Nono-chan really wanted to say
-was something else.</t>
+          <t>But it seemed that what Nono-chan really wanted to
+say was something else.</t>
         </is>
       </c>
       <c r="C720" t="n">

--- a/processed_ruby_restored_xlsx/sc218_ノノＡ：遊園地.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc218_ノノＡ：遊園地.ss.xlsx
@@ -1086,7 +1086,7 @@
       <c r="B41" s="1" t="inlineStr">
         <is>
           <t>I was sure they’d agree to splitting into groups, but
-it seems everyone thinks the same as Nono.</t>
+it seems everyone thinks the same as Monono.</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei？ It was decided by majority vote.」</t>
+          <t>Janitor-sensei？ It was decided by majority vote.</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1350,8 +1350,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>「That was a fun field trip, wasn't it,
-Janitor-sensei？」</t>
+          <t>That was a fun field trip, wasn't it, Janitor-sensei？</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1963,8 +1962,8 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... when it's just the two of us, Janitor-sensei
-gets mean...」</t>
+          <t>Ugh... when it's just the two of us, Janitor-sensei
+gets mean...</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2687,7 +2686,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>「What...? Right now...?」</t>
+          <t>What...? Right now...?</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2717,8 +2716,8 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... if you’re this close, I can’t hold back...
-Is that wrong？」</t>
+          <t>Yeah... if you’re this close, I can’t hold back... Is
+that wrong？</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2839,8 +2838,8 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>When I asked for a kiss in a clingy way, Nono-chan
-hesitated a bit, but to my surprise she nodded
+          <t>When he asked for a kiss in a clingy way, Nono-chan
+hesitated a bit, but to his surprise she nodded
 without much fuss.</t>
         </is>
       </c>
@@ -2961,8 +2960,8 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！ Chu-chu！ Nn-ah... nn！ Chuuu... ufuu... chu！
-Fwaaaaah！」</t>
+          <t>Smooch！ Chu-chu！ Nn-ah... nn！ Chuuu... ufuu... chu！
+Fwaaaaah！</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3024,8 +3023,8 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>「If you make too much noise, you'll wake everyone up,
-okay？」</t>
+          <t>If you make too much noise, you'll wake everyone up,
+okay？</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3055,8 +3054,8 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah... nn, nnh... chu！ H-haa... hup！ Chu, ah...
-chuk！」</t>
+          <t>Y-yeah... nn, nnh... chu！ H-haa... hup！ Chu, ah...
+chuk！</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3086,7 +3085,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>「Hold it, hold it... okay？ Chuu...」</t>
+          <t>Hold it, hold it... okay？ Chuu...</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3380,7 +3379,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh！ N, n~ngh！ Ah, fa... fuwah！ Ah！ Ha, ha！」</t>
+          <t>Nnngh！ N, n~ngh！ Ah, fa... fuwah！ Ah！ Ha, ha！</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3458,7 +3457,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>「Nn... yo—mui, in, se... chu, chuuu...」</t>
+          <t>Nn... yo—mui, in, se... chu, chuuu...</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3707,7 +3706,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>「Nn—！　Fuuah—！　Huh！　Fuuuh—！」</t>
+          <t>Nn—！　Fuuah—！　Huh！　Fuuuh—！</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -4443,8 +4442,8 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>「That's... Janitor-sensei, you are too！ Your penis...
-it's already rock hard, isn't it...！?」</t>
+          <t>That's... Janitor-sensei, you are too！ Your penis...
+it's already rock hard, isn't it...！?</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4615,7 +4614,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei... um, I...」</t>
+          <t>Janitor-sensei... um, I...</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -7768,7 +7767,7 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t>「J-Janitor-sensei...？ Are you okay...？」</t>
+          <t>J-Janitor-sensei...？ Are you okay...？</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -8242,8 +8241,8 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>「Fah, ahhh... Janitor-sensei... nngh... smooch！
-smooch！ smooch！」</t>
+          <t>Fah, ahhh... Janitor-sensei... nngh... smooch！
+smooch！ smooch！</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -8583,8 +8582,8 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>「Fu... fuu... I want Janitor-sensei to feel even
-better... nnngh」</t>
+          <t>Fu... fuu... I want Janitor-sensei to feel even
+better... nnngh</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8676,8 +8675,8 @@
       </c>
       <c r="B535" s="1" t="inlineStr">
         <is>
-          <t>「Nngh！ Hehe！ Janitor-sensei... such a naughty face...
-fah, smooch.」</t>
+          <t>Nngh！ Hehe！ Janitor-sensei... such a naughty face...
+fah, smooch.</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8817,7 +8816,7 @@
       <c r="B544" s="1" t="inlineStr">
         <is>
           <t>Maybe I'm getting used to inserting in this awkward
-position while we're kissing...？</t>
+position while we're kissing...？"</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -8847,8 +8846,8 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... Janitor-sensei... smooch, mmm...！ Ahh,
-uaaa... mmm, smooch.」</t>
+          <t>Mmm... Janitor-sensei... smooch, mmm...！ Ahh, uaaa...
+mmm, smooch.</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -9247,7 +9246,7 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh~!？　Ah!　Fuwaaaaah…!」</t>
+          <t>Nnngh~!？　Ah!　Fuwaaaaah…!</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -9782,8 +9781,8 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>After staring at each other for a long time, we share
-a light kiss.</t>
+          <t>After staring at each other for a long time, they
+share a light kiss.</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -9908,8 +9907,8 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haa...nh！ Nha！ Hyugo, hyu-go...ku！ Yes...yes,
-it's good！ Ha, aa...nnuu！」</t>
+          <t>Hah, haa...nh！ Nha！ Hyugo, hyu-go...ku！ Yes...yes,
+it」s good！ Ha, aa...nnuu！</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -10063,8 +10062,8 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>I lift her tiny body up and drive it deep, shallow,
-deep again and again.</t>
+          <t>He lifts her tiny body up and drives it deep,
+shallow, deep again and again.</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10353,7 +10352,7 @@
       </c>
       <c r="B644" s="1" t="inlineStr">
         <is>
-          <t>「Nnffuuuuah！？　Nnh！　Nnn—n！？」</t>
+          <t>Nnffuuuuah！？　Nnh！　Nnn—n！？</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -10664,7 +10663,7 @@
       <c r="B664" s="1" t="inlineStr">
         <is>
           <t>Her pussy twitched and pulsed in small jerks again
-and again as it stroked my penis.</t>
+and again as it stroked his penis.</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -11013,7 +11012,7 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, smooch…」</t>
+          <t>Mmm, smooch…</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -11028,7 +11027,7 @@
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>Gently stroking her head, I give her a soft kiss.</t>
+          <t>Gently stroking their head, I give them a soft kiss.</t>
         </is>
       </c>
       <c r="C688" t="n">
